--- a/public/templates/examples/A-173-AccountToRoleAssignmentRegister-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-173-AccountToRoleAssignmentRegister-EXAMPLE-L.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="0"/>
   <fonts count="9">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -319,12 +319,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1619250" cy="1619250"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -463,12 +463,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-173-AccountToRoleAssignmentRegister-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-173-AccountToRoleAssignmentRegister-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="Aptos"/>
@@ -183,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -239,6 +244,10 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,7 +732,7 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Username / ID</t>
@@ -786,18 +795,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
+      <c r="F12" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G12" s="23">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>ktran</t>
@@ -823,15 +828,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="F13" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G13" s="23">
+        <v>46174</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
@@ -860,18 +861,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
+      <c r="F14" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G14" s="23">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
           <t>mwebb</t>
@@ -897,18 +894,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
+      <c r="F15" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G15" s="23">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
           <t>svc-cad</t>
@@ -934,18 +927,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
+      <c r="F16" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G16" s="23">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>jtemp</t>
@@ -971,15 +960,11 @@
           <t>Suspended</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+      <c r="F17" s="23">
+        <v>46082</v>
+      </c>
+      <c r="G17" s="23">
+        <v>46113</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
@@ -1021,7 +1006,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-04-02)</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1019,6 @@
       <c r="B24" s="20" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1046,7 +1030,6 @@
       <c r="B25" s="20" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(E12:E21,"Active")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1058,7 +1041,6 @@
       <c r="B26" s="20" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIF(E12:E21,"Suspended")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -1070,7 +1052,6 @@
       <c r="B27" s="20" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIF(E12:E21,"Departed")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1086,8 +1067,7 @@
       </c>
       <c r="B29" s="20" t="n"/>
       <c r="C29" s="13">
-        <f>COUNTIF(G12:G21,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(G12:G21,"&lt;"&amp;DATE(2026,4,2))</f>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -1160,7 +1140,7 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="14" t="n"/>
     </row>
-    <row r="40" ht="46" customHeight="1">
+    <row r="40" ht="66.4" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Approving official (Executive Director)</t>
@@ -1176,13 +1156,11 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="46" customHeight="1">
+      <c r="D40" s="24">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="41" ht="66.4" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Owner (Information Security Analyst)</t>
@@ -1198,10 +1176,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D41" s="24">
+        <v>46082</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
@@ -1236,16 +1212,14 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="66.4" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
+      <c r="B45" s="23">
+        <v>46032</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
@@ -1261,11 +1235,11 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
     </row>
-    <row r="47" ht="58" customHeight="1">
-      <c r="A47" s="2" t="n"/>
+    <row r="47">
+      <c r="A47"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:G6"/>
@@ -1293,18 +1267,11 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E12:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"Active,Under Review,Retired,Decommissioned"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>